--- a/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
